--- a/TutorialsNinja/ExcelFiles/TestData.xlsx
+++ b/TutorialsNinja/ExcelFiles/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5A7CC0-16C7-45EE-8A9A-73617AAB3D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3632BBC5-F685-43FF-8CAF-6C186C9C1DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,9 +35,6 @@
     <t>ConfirmPassword</t>
   </si>
   <si>
-    <t>Demo</t>
-  </si>
-  <si>
     <t>Demo123</t>
   </si>
   <si>
@@ -50,10 +47,13 @@
     <t>admin.1@gmail.com</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>demouser@gmail.com</t>
+    <t>Harini</t>
+  </si>
+  <si>
+    <t>raja</t>
+  </si>
+  <si>
+    <t>harini12rg@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -434,7 +434,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -446,30 +446,30 @@
         <v>7639604120</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>9344960647</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
